--- a/outputs/monitor_xlsx/20260127.xlsx
+++ b/outputs/monitor_xlsx/20260127.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1107,40 +1110,35 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1193,12 +1191,7 @@
       <c r="N4" t="n">
         <v>1.25</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1236,12 +1229,7 @@
       <c r="M5" t="n">
         <v>-21110</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1294,12 +1282,7 @@
       <c r="N6" t="n">
         <v>-1.65</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1352,12 +1335,7 @@
       <c r="N7" t="n">
         <v>1.42</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1410,12 +1388,7 @@
       <c r="N8" t="n">
         <v>4.17</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1468,12 +1441,7 @@
       <c r="N9" t="n">
         <v>1.14</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1526,12 +1494,7 @@
       <c r="N10" t="n">
         <v>7.14</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1584,12 +1547,7 @@
       <c r="N11" t="n">
         <v>8.66</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1642,12 +1600,7 @@
       <c r="N12" t="n">
         <v>1.72</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1700,12 +1653,7 @@
       <c r="N13" t="n">
         <v>0.18</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1758,12 +1706,7 @@
       <c r="N14" t="n">
         <v>10.51</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1816,12 +1759,7 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1874,12 +1812,7 @@
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1932,12 +1865,7 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1990,12 +1918,7 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2048,12 +1971,7 @@
       <c r="N19" t="n">
         <v>10.49</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2106,11 +2024,6 @@
       <c r="N20" t="n">
         <v>-14.17</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2159,11 +2072,6 @@
       <c r="N21" t="n">
         <v>5.41</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2212,11 +2120,6 @@
       <c r="N22" t="n">
         <v>-10.11</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,11 +2168,6 @@
       <c r="N23" t="n">
         <v>-2.39</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2318,11 +2216,6 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2370,11 +2263,6 @@
       </c>
       <c r="N25" t="n">
         <v>-74.2</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260127.xlsx
+++ b/outputs/monitor_xlsx/20260127.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1152,44 +1149,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>73.05</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>1.11</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" s="7" t="n">
         <v>73059</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="7" t="n">
         <v>3729</v>
       </c>
-      <c r="G4" t="n">
-        <v>-106862</v>
-      </c>
       <c r="H4" t="n">
+        <v>-56007</v>
+      </c>
+      <c r="I4" t="n">
         <v>282</v>
       </c>
-      <c r="I4" t="n">
-        <v>5300</v>
-      </c>
       <c r="J4" t="n">
+        <v>5582</v>
+      </c>
+      <c r="K4" t="n">
         <v>11591</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>6946</v>
       </c>
-      <c r="L4" t="n">
-        <v>38028</v>
-      </c>
       <c r="M4" t="n">
+        <v>37084</v>
+      </c>
+      <c r="N4" t="n">
         <v>-3958815</v>
       </c>
-      <c r="N4" t="n">
-        <v>1.25</v>
+      <c r="O4" t="n">
+        <v>2.19</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1246,41 +1248,46 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>1015</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="E6" s="7" t="n">
         <v>-0.49</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" s="7" t="n">
         <v>2498</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="7" t="n">
         <v>539</v>
       </c>
-      <c r="G6" t="n">
-        <v>1949</v>
-      </c>
       <c r="H6" t="n">
+        <v>1182</v>
+      </c>
+      <c r="I6" t="n">
         <v>-154</v>
       </c>
-      <c r="I6" t="n">
-        <v>-267</v>
-      </c>
       <c r="J6" t="n">
+        <v>-484</v>
+      </c>
+      <c r="K6" t="n">
         <v>56</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2784</v>
       </c>
-      <c r="L6" t="n">
-        <v>14628</v>
-      </c>
       <c r="M6" t="n">
+        <v>14352</v>
+      </c>
+      <c r="N6" t="n">
         <v>-78616</v>
       </c>
-      <c r="N6" t="n">
-        <v>-1.65</v>
+      <c r="O6" t="n">
+        <v>8.859999999999999</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1352,41 +1359,46 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>1250</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>1.63</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" s="6" t="n">
         <v>9071</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>-39</v>
       </c>
-      <c r="G8" t="n">
-        <v>1934</v>
-      </c>
       <c r="H8" t="n">
+        <v>1590</v>
+      </c>
+      <c r="I8" t="n">
         <v>383</v>
       </c>
-      <c r="I8" t="n">
-        <v>1021</v>
-      </c>
       <c r="J8" t="n">
+        <v>1257</v>
+      </c>
+      <c r="K8" t="n">
         <v>165</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>8127</v>
       </c>
-      <c r="L8" t="n">
-        <v>42784</v>
-      </c>
       <c r="M8" t="n">
+        <v>42571</v>
+      </c>
+      <c r="N8" t="n">
         <v>-648553</v>
       </c>
-      <c r="N8" t="n">
-        <v>4.17</v>
+      <c r="O8" t="n">
+        <v>11.39</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1405,41 +1417,46 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>1780</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>1.42</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" s="7" t="n">
         <v>32183</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="G9" s="7" t="n">
         <v>6704</v>
       </c>
-      <c r="G9" t="n">
-        <v>-37696</v>
-      </c>
       <c r="H9" t="n">
+        <v>-25600</v>
+      </c>
+      <c r="I9" t="n">
         <v>-285</v>
       </c>
-      <c r="I9" t="n">
-        <v>-269</v>
-      </c>
       <c r="J9" t="n">
+        <v>-532</v>
+      </c>
+      <c r="K9" t="n">
         <v>632</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>19791</v>
       </c>
-      <c r="L9" t="n">
-        <v>104745</v>
-      </c>
       <c r="M9" t="n">
+        <v>103814</v>
+      </c>
+      <c r="N9" t="n">
         <v>-6482804</v>
       </c>
-      <c r="N9" t="n">
-        <v>1.14</v>
+      <c r="O9" t="n">
+        <v>2.78</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1511,41 +1528,46 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>1820</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" s="7" t="n">
         <v>3568</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="G11" s="7" t="n">
         <v>916</v>
       </c>
-      <c r="G11" t="n">
-        <v>5043</v>
-      </c>
       <c r="H11" t="n">
+        <v>4711</v>
+      </c>
+      <c r="I11" t="n">
         <v>-15</v>
       </c>
-      <c r="I11" t="n">
-        <v>-965</v>
-      </c>
       <c r="J11" t="n">
+        <v>-798</v>
+      </c>
+      <c r="K11" t="n">
         <v>121</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>1993</v>
       </c>
-      <c r="L11" t="n">
-        <v>11236</v>
-      </c>
       <c r="M11" t="n">
+        <v>10858</v>
+      </c>
+      <c r="N11" t="n">
         <v>-89481</v>
       </c>
-      <c r="N11" t="n">
-        <v>8.66</v>
+      <c r="O11" t="n">
+        <v>10.81</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1670,41 +1692,46 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>1430</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" s="7" t="n">
         <v>2233</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>169</v>
       </c>
-      <c r="G14" t="n">
-        <v>-339</v>
-      </c>
       <c r="H14" t="n">
+        <v>365</v>
+      </c>
+      <c r="I14" t="n">
         <v>-5</v>
       </c>
-      <c r="I14" t="n">
-        <v>451</v>
-      </c>
       <c r="J14" t="n">
+        <v>378</v>
+      </c>
+      <c r="K14" t="n">
         <v>32</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>5208</v>
       </c>
-      <c r="L14" t="n">
-        <v>25659</v>
-      </c>
       <c r="M14" t="n">
+        <v>25474</v>
+      </c>
+      <c r="N14" t="n">
         <v>-19157</v>
       </c>
-      <c r="N14" t="n">
-        <v>10.51</v>
+      <c r="O14" t="n">
+        <v>7.9</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1723,42 +1750,47 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="E15" t="n">
-        <v>905</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2.16</v>
       </c>
       <c r="F15" s="6" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G15" s="6" t="n">
         <v>-1082</v>
       </c>
-      <c r="G15" t="n">
-        <v>1970</v>
-      </c>
       <c r="H15" t="n">
+        <v>-370</v>
+      </c>
+      <c r="I15" t="n">
         <v>249</v>
       </c>
-      <c r="I15" t="n">
-        <v>871</v>
-      </c>
       <c r="J15" t="n">
+        <v>1120</v>
+      </c>
+      <c r="K15" t="n">
         <v>-90</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>306</v>
       </c>
-      <c r="L15" t="n">
-        <v>-738</v>
-      </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-208</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1882,42 +1914,47 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>318.5</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="E18" t="n">
-        <v>20497</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>586</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>9.94</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>312</v>
       </c>
-      <c r="G18" t="n">
-        <v>-9351</v>
-      </c>
       <c r="H18" t="n">
+        <v>-8724</v>
+      </c>
+      <c r="I18" t="n">
         <v>13</v>
       </c>
-      <c r="I18" t="n">
-        <v>4337</v>
-      </c>
       <c r="J18" t="n">
+        <v>4350</v>
+      </c>
+      <c r="K18" t="n">
         <v>179</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>206</v>
       </c>
-      <c r="L18" t="n">
-        <v>408</v>
-      </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1625</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2132,41 +2169,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
         <v>1155</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>0.43</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" s="7" t="n">
         <v>3771</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="G23" s="7" t="n">
         <v>330</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>994</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>-27</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>-1683</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>27</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2566</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>12848</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-140162</v>
       </c>
-      <c r="N23" t="n">
-        <v>-2.39</v>
+      <c r="O23" t="n">
+        <v>-3.06</v>
       </c>
     </row>
     <row r="24">
@@ -2180,42 +2222,47 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>962</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-16</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>60</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-5</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>75</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>203</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2263,6 +2310,218 @@
       </c>
       <c r="N25" t="n">
         <v>-74.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1972</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>464</v>
+      </c>
+      <c r="H26" t="n">
+        <v>510</v>
+      </c>
+      <c r="I26" t="n">
+        <v>57</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>24</v>
+      </c>
+      <c r="L26" t="n">
+        <v>918</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4548</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-106258</v>
+      </c>
+      <c r="O26" t="n">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>4275</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>714</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>176</v>
+      </c>
+      <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>359</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1837</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-8866</v>
+      </c>
+      <c r="O27" t="n">
+        <v>17.16</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-79</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1151</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-39</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-162</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>233</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>4805</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-524</v>
+      </c>
+      <c r="H29" t="n">
+        <v>321</v>
+      </c>
+      <c r="I29" t="n">
+        <v>125</v>
+      </c>
+      <c r="J29" t="n">
+        <v>498</v>
+      </c>
+      <c r="K29" t="n">
+        <v>66</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6363</v>
+      </c>
+      <c r="M29" t="n">
+        <v>32238</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-21432</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.56</v>
       </c>
     </row>
   </sheetData>
